--- a/Claude outputs/HSSE-Fusion4_Author-Tag-per-Modul.xlsx
+++ b/Claude outputs/HSSE-Fusion4_Author-Tag-per-Modul.xlsx
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -997,19 +997,79 @@
       </c>
       <c r="D25" s="10" t="inlineStr"/>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>Catatan: baris hijau muda = modul/tahap terbuka, boleh diisi siapa saja tanpa Author tag khusus. Sumber: HSSE-Fusion4 (per 04 Sep 2026).</t>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Management Walk Through (MWT)</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Buat Jadwal MWT (Rencana kunjungan)</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Admin MWT</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>HSE Admin/koordinator yang bikin jadwal &amp; tentukan area + tanggal kunjungan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Isi Kunjungan MWT (gabung sesi &amp; submit observasi)</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Management Walkthrough</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Multi-peserta independen -- siapapun ber-tag ini boleh join sesi yang masih Terjadwal/Berlangsung</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="12" t="n"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Tutup sesi MWT (force-close)</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Admin MWT</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Backstop kalau ada peserta lupa centang "Tandai Selesai" pas submit kunjungannya sendiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>Catatan: baris hijau muda = modul/tahap terbuka, boleh diisi siapa saja tanpa Author tag khusus. Sumber: HSSE-Fusion4 (per 05 Sep 2026).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A26:A28"/>
     <mergeCell ref="A5:A9"/>
     <mergeCell ref="A16:A20"/>
+    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A10:A14"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A2:D2"/>
